--- a/docs/build/lakeshore-enterprise-context/source/06_it_systems_architecture/security_tools.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/06_it_systems_architecture/security_tools.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Deployed</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Deployed</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Deployed</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
